--- a/reporte_habitos_PRO.xlsx
+++ b/reporte_habitos_PRO.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +555,48 @@
         <v>46112</v>
       </c>
       <c r="J3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>lectura</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Mente</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>15 paginas diarias</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="J4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -569,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,10 +696,10 @@
         </is>
       </c>
       <c r="C4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -683,6 +725,26 @@
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lectura</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -748,23 +810,23 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
         <v>5</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7</v>
       </c>
       <c r="G2" t="n">
         <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>borre mis contenido por que no se si sea buena idea tampoco es que me de beneicio</t>
+          <t>borre mis contenido por que no se si sea buena idea tampoco es que me de beneicio, lei un poco sobre el libro de samauel aun weon e hice este sofware para producticidad</t>
         </is>
       </c>
     </row>
